--- a/lr2/excel_solution.xlsx
+++ b/lr2/excel_solution.xlsx
@@ -197,7 +197,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>f(x) и точки испытаний метода ломаных</a:t>
+              <a:t>W(x) и верхние вершины ломаной</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -209,7 +209,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>f(x)</v>
+            <v>W(x)</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -240,7 +240,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>точки испытаний</v>
+            <v>верхние вершины u_n</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -259,12 +259,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Метод ломаных'!$G$11:$G$55</f>
+              <f>'Метод ломаных'!$G$11:$G$60</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Метод ломаных'!$K$11:$K$55</f>
+              <f>'Метод ломаных'!$I$11:$I$60</f>
             </numRef>
           </yVal>
         </ser>
@@ -649,11 +649,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -661,16 +661,15 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ЛР2. Метод ломаных — ручное прохождение: f(x) = x + sin(3.14159·x) на [-3; 3]</t>
+          <t>ЛР2. Метод ломаных — ручное прохождение: W(x) = x + sin(3.14159·x) на [-3; 3]</t>
         </is>
       </c>
     </row>
@@ -685,7 +684,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>L = max|f'(x)| = max|1 + π·cos(πx)| = 1 + π.</t>
+          <t>L = max|W'(x)| = max|1 + π·cos(πx)| = 1 + π.  Стартовые итерации: u0 = a, u1 = b.</t>
         </is>
       </c>
     </row>
@@ -700,7 +699,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Нижняя вершина ломаной на [xл; xп]:  x̂ = (xл + xп)/2 + (f(xл) − f(xп))/(2L),   p̂ = (f(xл) + f(xп))/2 − L(xп − xл)/2.</t>
+          <t>Пересечение галочек соседних верхних вершин uл &lt; uп:  u = (W(uл) − W(uп))/(2L) + (uл + uп)/2,  p(u) = (W(uл) + W(uп))/2 − L(uп − uл)/2.</t>
         </is>
       </c>
     </row>
@@ -716,7 +715,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>На каждом шаге берём самую низкую из ещё не использованных вершин (её интервал вписан в строку),</t>
+          <t>На каждой итерации берём самую низкую нижнюю вершину ломаной (её верхние вершины вписаны в строку) — это u_n,</t>
         </is>
       </c>
     </row>
@@ -731,14 +730,14 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>вычисляем f(x̂) — это новая точка испытания; её вершина заменяется двумя новыми (слева и справа).</t>
+          <t>вычисляем W(u_n) — новая верхняя вершина; её галочка g_n заменяет нижнюю вершину двумя новыми (слева и справа).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>f(a)</t>
+          <t>W(a)</t>
         </is>
       </c>
       <c r="B7" s="3">
@@ -747,14 +746,14 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Остановка: рекорд f* − p̂ ≤ eps (p̂ — минимум ломаной, f* — лучшее найденное значение).</t>
+          <t>Остановка (как в лекции): W(u_n) − p_{n−1}(u_n) &lt; eps; ответ u* = u_n, W* = W(u_n).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>f(b)</t>
+          <t>W(b)</t>
         </is>
       </c>
       <c r="B8" s="3">
@@ -765,65 +764,60 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>точки (№)</t>
+          <t>верхние вершины (№)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>xл</t>
+          <t>uл</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>f(xл)</t>
+          <t>W(uл)</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>xп</t>
+          <t>uп</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>f(xп)</t>
+          <t>W(uп)</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>x̂ — вершина</t>
+          <t>u_n — пересечение</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>p̂ — высота</t>
+          <t>p_{n−1}(u_n)</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>рекорд f*</t>
+          <t>W(u_n)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>f* − p̂</t>
+          <t>W(u_n) − p</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>f(x̂)</t>
+          <t>№ точки u</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>№ новой точки</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>статус</t>
         </is>
@@ -855,7 +849,7 @@
         <v/>
       </c>
       <c r="G11" s="7">
-        <f>(C11+E11)/2+(D11-F11)/(2*$B$5)</f>
+        <f>(D11-F11)/(2*$B$5)+(C11+E11)/2</f>
         <v/>
       </c>
       <c r="H11" s="7">
@@ -863,22 +857,18 @@
         <v/>
       </c>
       <c r="I11" s="7">
-        <f>MIN($B$7,$B$8,K$10:K10)</f>
+        <f>G11+SIN(3.14159*G11)</f>
         <v/>
       </c>
       <c r="J11" s="7">
         <f>I11-H11</f>
         <v/>
       </c>
-      <c r="K11" s="7">
-        <f>G11+SIN(3.14159*G11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="6">
-        <f>IF(J11&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L11" s="6">
+        <f>IF(J11&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -896,7 +886,7 @@
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>$K$11</f>
+        <f>$I$11</f>
         <v/>
       </c>
       <c r="E12" s="7">
@@ -908,7 +898,7 @@
         <v/>
       </c>
       <c r="G12" s="7">
-        <f>(C12+E12)/2+(D12-F12)/(2*$B$5)</f>
+        <f>(D12-F12)/(2*$B$5)+(C12+E12)/2</f>
         <v/>
       </c>
       <c r="H12" s="7">
@@ -916,22 +906,18 @@
         <v/>
       </c>
       <c r="I12" s="7">
-        <f>MIN($B$7,$B$8,K$10:K11)</f>
+        <f>G12+SIN(3.14159*G12)</f>
         <v/>
       </c>
       <c r="J12" s="7">
         <f>I12-H12</f>
         <v/>
       </c>
-      <c r="K12" s="7">
-        <f>G12+SIN(3.14159*G12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="M12" s="6">
-        <f>IF(J12&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L12" s="6">
+        <f>IF(J12&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -957,11 +943,11 @@
         <v/>
       </c>
       <c r="F13" s="7">
-        <f>$K$11</f>
+        <f>$I$11</f>
         <v/>
       </c>
       <c r="G13" s="7">
-        <f>(C13+E13)/2+(D13-F13)/(2*$B$5)</f>
+        <f>(D13-F13)/(2*$B$5)+(C13+E13)/2</f>
         <v/>
       </c>
       <c r="H13" s="7">
@@ -969,22 +955,18 @@
         <v/>
       </c>
       <c r="I13" s="7">
-        <f>MIN($B$7,$B$8,K$10:K12)</f>
+        <f>G13+SIN(3.14159*G13)</f>
         <v/>
       </c>
       <c r="J13" s="7">
         <f>I13-H13</f>
         <v/>
       </c>
-      <c r="K13" s="7">
-        <f>G13+SIN(3.14159*G13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="6" t="n">
+      <c r="K13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="M13" s="6">
-        <f>IF(J13&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L13" s="6">
+        <f>IF(J13&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1010,11 +992,11 @@
         <v/>
       </c>
       <c r="F14" s="7">
-        <f>$K$13</f>
+        <f>$I$13</f>
         <v/>
       </c>
       <c r="G14" s="7">
-        <f>(C14+E14)/2+(D14-F14)/(2*$B$5)</f>
+        <f>(D14-F14)/(2*$B$5)+(C14+E14)/2</f>
         <v/>
       </c>
       <c r="H14" s="7">
@@ -1022,22 +1004,18 @@
         <v/>
       </c>
       <c r="I14" s="7">
-        <f>MIN($B$7,$B$8,K$10:K13)</f>
+        <f>G14+SIN(3.14159*G14)</f>
         <v/>
       </c>
       <c r="J14" s="7">
         <f>I14-H14</f>
         <v/>
       </c>
-      <c r="K14" s="7">
-        <f>G14+SIN(3.14159*G14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="6" t="n">
+      <c r="K14" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="M14" s="6">
-        <f>IF(J14&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L14" s="6">
+        <f>IF(J14&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1055,7 +1033,7 @@
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>$K$13</f>
+        <f>$I$13</f>
         <v/>
       </c>
       <c r="E15" s="7">
@@ -1063,11 +1041,11 @@
         <v/>
       </c>
       <c r="F15" s="7">
-        <f>$K$11</f>
+        <f>$I$11</f>
         <v/>
       </c>
       <c r="G15" s="7">
-        <f>(C15+E15)/2+(D15-F15)/(2*$B$5)</f>
+        <f>(D15-F15)/(2*$B$5)+(C15+E15)/2</f>
         <v/>
       </c>
       <c r="H15" s="7">
@@ -1075,22 +1053,18 @@
         <v/>
       </c>
       <c r="I15" s="7">
-        <f>MIN($B$7,$B$8,K$10:K14)</f>
+        <f>G15+SIN(3.14159*G15)</f>
         <v/>
       </c>
       <c r="J15" s="7">
         <f>I15-H15</f>
         <v/>
       </c>
-      <c r="K15" s="7">
-        <f>G15+SIN(3.14159*G15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="M15" s="6">
-        <f>IF(J15&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L15" s="6">
+        <f>IF(J15&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1116,11 +1090,11 @@
         <v/>
       </c>
       <c r="F16" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="G16" s="7">
-        <f>(C16+E16)/2+(D16-F16)/(2*$B$5)</f>
+        <f>(D16-F16)/(2*$B$5)+(C16+E16)/2</f>
         <v/>
       </c>
       <c r="H16" s="7">
@@ -1128,22 +1102,18 @@
         <v/>
       </c>
       <c r="I16" s="7">
-        <f>MIN($B$7,$B$8,K$10:K15)</f>
+        <f>G16+SIN(3.14159*G16)</f>
         <v/>
       </c>
       <c r="J16" s="7">
         <f>I16-H16</f>
         <v/>
       </c>
-      <c r="K16" s="7">
-        <f>G16+SIN(3.14159*G16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="6" t="n">
+      <c r="K16" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="M16" s="6">
-        <f>IF(J16&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L16" s="6">
+        <f>IF(J16&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1161,7 +1131,7 @@
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="E17" s="7">
@@ -1169,11 +1139,11 @@
         <v/>
       </c>
       <c r="F17" s="7">
-        <f>$K$13</f>
+        <f>$I$13</f>
         <v/>
       </c>
       <c r="G17" s="7">
-        <f>(C17+E17)/2+(D17-F17)/(2*$B$5)</f>
+        <f>(D17-F17)/(2*$B$5)+(C17+E17)/2</f>
         <v/>
       </c>
       <c r="H17" s="7">
@@ -1181,22 +1151,18 @@
         <v/>
       </c>
       <c r="I17" s="7">
-        <f>MIN($B$7,$B$8,K$10:K16)</f>
+        <f>G17+SIN(3.14159*G17)</f>
         <v/>
       </c>
       <c r="J17" s="7">
         <f>I17-H17</f>
         <v/>
       </c>
-      <c r="K17" s="7">
-        <f>G17+SIN(3.14159*G17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="6" t="n">
+      <c r="K17" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="M17" s="6">
-        <f>IF(J17&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L17" s="6">
+        <f>IF(J17&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1214,7 +1180,7 @@
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="E18" s="7">
@@ -1222,11 +1188,11 @@
         <v/>
       </c>
       <c r="F18" s="7">
-        <f>$K$17</f>
+        <f>$I$17</f>
         <v/>
       </c>
       <c r="G18" s="7">
-        <f>(C18+E18)/2+(D18-F18)/(2*$B$5)</f>
+        <f>(D18-F18)/(2*$B$5)+(C18+E18)/2</f>
         <v/>
       </c>
       <c r="H18" s="7">
@@ -1234,22 +1200,18 @@
         <v/>
       </c>
       <c r="I18" s="7">
-        <f>MIN($B$7,$B$8,K$10:K17)</f>
+        <f>G18+SIN(3.14159*G18)</f>
         <v/>
       </c>
       <c r="J18" s="7">
         <f>I18-H18</f>
         <v/>
       </c>
-      <c r="K18" s="7">
-        <f>G18+SIN(3.14159*G18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="6" t="n">
+      <c r="K18" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="M18" s="6">
-        <f>IF(J18&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L18" s="6">
+        <f>IF(J18&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1267,7 +1229,7 @@
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>$K$17</f>
+        <f>$I$17</f>
         <v/>
       </c>
       <c r="E19" s="7">
@@ -1275,11 +1237,11 @@
         <v/>
       </c>
       <c r="F19" s="7">
-        <f>$K$13</f>
+        <f>$I$13</f>
         <v/>
       </c>
       <c r="G19" s="7">
-        <f>(C19+E19)/2+(D19-F19)/(2*$B$5)</f>
+        <f>(D19-F19)/(2*$B$5)+(C19+E19)/2</f>
         <v/>
       </c>
       <c r="H19" s="7">
@@ -1287,22 +1249,18 @@
         <v/>
       </c>
       <c r="I19" s="7">
-        <f>MIN($B$7,$B$8,K$10:K18)</f>
+        <f>G19+SIN(3.14159*G19)</f>
         <v/>
       </c>
       <c r="J19" s="7">
         <f>I19-H19</f>
         <v/>
       </c>
-      <c r="K19" s="7">
-        <f>G19+SIN(3.14159*G19)</f>
-        <v/>
-      </c>
-      <c r="L19" s="6" t="n">
+      <c r="K19" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="M19" s="6">
-        <f>IF(J19&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L19" s="6">
+        <f>IF(J19&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1328,11 +1286,11 @@
         <v/>
       </c>
       <c r="F20" s="7">
-        <f>$K$16</f>
+        <f>$I$16</f>
         <v/>
       </c>
       <c r="G20" s="7">
-        <f>(C20+E20)/2+(D20-F20)/(2*$B$5)</f>
+        <f>(D20-F20)/(2*$B$5)+(C20+E20)/2</f>
         <v/>
       </c>
       <c r="H20" s="7">
@@ -1340,22 +1298,18 @@
         <v/>
       </c>
       <c r="I20" s="7">
-        <f>MIN($B$7,$B$8,K$10:K19)</f>
+        <f>G20+SIN(3.14159*G20)</f>
         <v/>
       </c>
       <c r="J20" s="7">
         <f>I20-H20</f>
         <v/>
       </c>
-      <c r="K20" s="7">
-        <f>G20+SIN(3.14159*G20)</f>
-        <v/>
-      </c>
-      <c r="L20" s="6" t="n">
+      <c r="K20" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="M20" s="6">
-        <f>IF(J20&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L20" s="6">
+        <f>IF(J20&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1373,7 +1327,7 @@
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>$K$16</f>
+        <f>$I$16</f>
         <v/>
       </c>
       <c r="E21" s="7">
@@ -1381,11 +1335,11 @@
         <v/>
       </c>
       <c r="F21" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="G21" s="7">
-        <f>(C21+E21)/2+(D21-F21)/(2*$B$5)</f>
+        <f>(D21-F21)/(2*$B$5)+(C21+E21)/2</f>
         <v/>
       </c>
       <c r="H21" s="7">
@@ -1393,22 +1347,18 @@
         <v/>
       </c>
       <c r="I21" s="7">
-        <f>MIN($B$7,$B$8,K$10:K20)</f>
+        <f>G21+SIN(3.14159*G21)</f>
         <v/>
       </c>
       <c r="J21" s="7">
         <f>I21-H21</f>
         <v/>
       </c>
-      <c r="K21" s="7">
-        <f>G21+SIN(3.14159*G21)</f>
-        <v/>
-      </c>
-      <c r="L21" s="6" t="n">
+      <c r="K21" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="M21" s="6">
-        <f>IF(J21&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L21" s="6">
+        <f>IF(J21&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1426,7 +1376,7 @@
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="E22" s="7">
@@ -1434,11 +1384,11 @@
         <v/>
       </c>
       <c r="F22" s="7">
-        <f>$K$18</f>
+        <f>$I$18</f>
         <v/>
       </c>
       <c r="G22" s="7">
-        <f>(C22+E22)/2+(D22-F22)/(2*$B$5)</f>
+        <f>(D22-F22)/(2*$B$5)+(C22+E22)/2</f>
         <v/>
       </c>
       <c r="H22" s="7">
@@ -1446,22 +1396,18 @@
         <v/>
       </c>
       <c r="I22" s="7">
-        <f>MIN($B$7,$B$8,K$10:K21)</f>
+        <f>G22+SIN(3.14159*G22)</f>
         <v/>
       </c>
       <c r="J22" s="7">
         <f>I22-H22</f>
         <v/>
       </c>
-      <c r="K22" s="7">
-        <f>G22+SIN(3.14159*G22)</f>
-        <v/>
-      </c>
-      <c r="L22" s="6" t="n">
+      <c r="K22" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="M22" s="6">
-        <f>IF(J22&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L22" s="6">
+        <f>IF(J22&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1479,7 +1425,7 @@
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>$K$18</f>
+        <f>$I$18</f>
         <v/>
       </c>
       <c r="E23" s="7">
@@ -1487,11 +1433,11 @@
         <v/>
       </c>
       <c r="F23" s="7">
-        <f>$K$17</f>
+        <f>$I$17</f>
         <v/>
       </c>
       <c r="G23" s="7">
-        <f>(C23+E23)/2+(D23-F23)/(2*$B$5)</f>
+        <f>(D23-F23)/(2*$B$5)+(C23+E23)/2</f>
         <v/>
       </c>
       <c r="H23" s="7">
@@ -1499,22 +1445,18 @@
         <v/>
       </c>
       <c r="I23" s="7">
-        <f>MIN($B$7,$B$8,K$10:K22)</f>
+        <f>G23+SIN(3.14159*G23)</f>
         <v/>
       </c>
       <c r="J23" s="7">
         <f>I23-H23</f>
         <v/>
       </c>
-      <c r="K23" s="7">
-        <f>G23+SIN(3.14159*G23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="M23" s="6">
-        <f>IF(J23&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L23" s="6">
+        <f>IF(J23&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1532,7 +1474,7 @@
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>$K$16</f>
+        <f>$I$16</f>
         <v/>
       </c>
       <c r="E24" s="7">
@@ -1540,11 +1482,11 @@
         <v/>
       </c>
       <c r="F24" s="7">
-        <f>$K$21</f>
+        <f>$I$21</f>
         <v/>
       </c>
       <c r="G24" s="7">
-        <f>(C24+E24)/2+(D24-F24)/(2*$B$5)</f>
+        <f>(D24-F24)/(2*$B$5)+(C24+E24)/2</f>
         <v/>
       </c>
       <c r="H24" s="7">
@@ -1552,22 +1494,18 @@
         <v/>
       </c>
       <c r="I24" s="7">
-        <f>MIN($B$7,$B$8,K$10:K23)</f>
+        <f>G24+SIN(3.14159*G24)</f>
         <v/>
       </c>
       <c r="J24" s="7">
         <f>I24-H24</f>
         <v/>
       </c>
-      <c r="K24" s="7">
-        <f>G24+SIN(3.14159*G24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="M24" s="6">
-        <f>IF(J24&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L24" s="6">
+        <f>IF(J24&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1585,7 +1523,7 @@
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>$K$21</f>
+        <f>$I$21</f>
         <v/>
       </c>
       <c r="E25" s="7">
@@ -1593,11 +1531,11 @@
         <v/>
       </c>
       <c r="F25" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="G25" s="7">
-        <f>(C25+E25)/2+(D25-F25)/(2*$B$5)</f>
+        <f>(D25-F25)/(2*$B$5)+(C25+E25)/2</f>
         <v/>
       </c>
       <c r="H25" s="7">
@@ -1605,22 +1543,18 @@
         <v/>
       </c>
       <c r="I25" s="7">
-        <f>MIN($B$7,$B$8,K$10:K24)</f>
+        <f>G25+SIN(3.14159*G25)</f>
         <v/>
       </c>
       <c r="J25" s="7">
         <f>I25-H25</f>
         <v/>
       </c>
-      <c r="K25" s="7">
-        <f>G25+SIN(3.14159*G25)</f>
-        <v/>
-      </c>
-      <c r="L25" s="6" t="n">
+      <c r="K25" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="M25" s="6">
-        <f>IF(J25&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L25" s="6">
+        <f>IF(J25&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1638,7 +1572,7 @@
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="E26" s="7">
@@ -1646,11 +1580,11 @@
         <v/>
       </c>
       <c r="F26" s="7">
-        <f>$K$22</f>
+        <f>$I$22</f>
         <v/>
       </c>
       <c r="G26" s="7">
-        <f>(C26+E26)/2+(D26-F26)/(2*$B$5)</f>
+        <f>(D26-F26)/(2*$B$5)+(C26+E26)/2</f>
         <v/>
       </c>
       <c r="H26" s="7">
@@ -1658,22 +1592,18 @@
         <v/>
       </c>
       <c r="I26" s="7">
-        <f>MIN($B$7,$B$8,K$10:K25)</f>
+        <f>G26+SIN(3.14159*G26)</f>
         <v/>
       </c>
       <c r="J26" s="7">
         <f>I26-H26</f>
         <v/>
       </c>
-      <c r="K26" s="7">
-        <f>G26+SIN(3.14159*G26)</f>
-        <v/>
-      </c>
-      <c r="L26" s="6" t="n">
+      <c r="K26" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="M26" s="6">
-        <f>IF(J26&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L26" s="6">
+        <f>IF(J26&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1691,7 +1621,7 @@
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>$K$22</f>
+        <f>$I$22</f>
         <v/>
       </c>
       <c r="E27" s="7">
@@ -1699,11 +1629,11 @@
         <v/>
       </c>
       <c r="F27" s="7">
-        <f>$K$18</f>
+        <f>$I$18</f>
         <v/>
       </c>
       <c r="G27" s="7">
-        <f>(C27+E27)/2+(D27-F27)/(2*$B$5)</f>
+        <f>(D27-F27)/(2*$B$5)+(C27+E27)/2</f>
         <v/>
       </c>
       <c r="H27" s="7">
@@ -1711,22 +1641,18 @@
         <v/>
       </c>
       <c r="I27" s="7">
-        <f>MIN($B$7,$B$8,K$10:K26)</f>
+        <f>G27+SIN(3.14159*G27)</f>
         <v/>
       </c>
       <c r="J27" s="7">
         <f>I27-H27</f>
         <v/>
       </c>
-      <c r="K27" s="7">
-        <f>G27+SIN(3.14159*G27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="6" t="n">
+      <c r="K27" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="6">
-        <f>IF(J27&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L27" s="6">
+        <f>IF(J27&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1744,7 +1670,7 @@
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>$K$18</f>
+        <f>$I$18</f>
         <v/>
       </c>
       <c r="E28" s="7">
@@ -1752,11 +1678,11 @@
         <v/>
       </c>
       <c r="F28" s="7">
-        <f>$K$23</f>
+        <f>$I$23</f>
         <v/>
       </c>
       <c r="G28" s="7">
-        <f>(C28+E28)/2+(D28-F28)/(2*$B$5)</f>
+        <f>(D28-F28)/(2*$B$5)+(C28+E28)/2</f>
         <v/>
       </c>
       <c r="H28" s="7">
@@ -1764,22 +1690,18 @@
         <v/>
       </c>
       <c r="I28" s="7">
-        <f>MIN($B$7,$B$8,K$10:K27)</f>
+        <f>G28+SIN(3.14159*G28)</f>
         <v/>
       </c>
       <c r="J28" s="7">
         <f>I28-H28</f>
         <v/>
       </c>
-      <c r="K28" s="7">
-        <f>G28+SIN(3.14159*G28)</f>
-        <v/>
-      </c>
-      <c r="L28" s="6" t="n">
+      <c r="K28" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="M28" s="6">
-        <f>IF(J28&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L28" s="6">
+        <f>IF(J28&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1797,7 +1719,7 @@
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>$K$23</f>
+        <f>$I$23</f>
         <v/>
       </c>
       <c r="E29" s="7">
@@ -1805,11 +1727,11 @@
         <v/>
       </c>
       <c r="F29" s="7">
-        <f>$K$17</f>
+        <f>$I$17</f>
         <v/>
       </c>
       <c r="G29" s="7">
-        <f>(C29+E29)/2+(D29-F29)/(2*$B$5)</f>
+        <f>(D29-F29)/(2*$B$5)+(C29+E29)/2</f>
         <v/>
       </c>
       <c r="H29" s="7">
@@ -1817,22 +1739,18 @@
         <v/>
       </c>
       <c r="I29" s="7">
-        <f>MIN($B$7,$B$8,K$10:K28)</f>
+        <f>G29+SIN(3.14159*G29)</f>
         <v/>
       </c>
       <c r="J29" s="7">
         <f>I29-H29</f>
         <v/>
       </c>
-      <c r="K29" s="7">
-        <f>G29+SIN(3.14159*G29)</f>
-        <v/>
-      </c>
-      <c r="L29" s="6" t="n">
+      <c r="K29" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="M29" s="6">
-        <f>IF(J29&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L29" s="6">
+        <f>IF(J29&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1850,7 +1768,7 @@
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>$K$21</f>
+        <f>$I$21</f>
         <v/>
       </c>
       <c r="E30" s="7">
@@ -1858,11 +1776,11 @@
         <v/>
       </c>
       <c r="F30" s="7">
-        <f>$K$25</f>
+        <f>$I$25</f>
         <v/>
       </c>
       <c r="G30" s="7">
-        <f>(C30+E30)/2+(D30-F30)/(2*$B$5)</f>
+        <f>(D30-F30)/(2*$B$5)+(C30+E30)/2</f>
         <v/>
       </c>
       <c r="H30" s="7">
@@ -1870,22 +1788,18 @@
         <v/>
       </c>
       <c r="I30" s="7">
-        <f>MIN($B$7,$B$8,K$10:K29)</f>
+        <f>G30+SIN(3.14159*G30)</f>
         <v/>
       </c>
       <c r="J30" s="7">
         <f>I30-H30</f>
         <v/>
       </c>
-      <c r="K30" s="7">
-        <f>G30+SIN(3.14159*G30)</f>
-        <v/>
-      </c>
-      <c r="L30" s="6" t="n">
+      <c r="K30" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="M30" s="6">
-        <f>IF(J30&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L30" s="6">
+        <f>IF(J30&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1903,7 +1817,7 @@
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>$K$25</f>
+        <f>$I$25</f>
         <v/>
       </c>
       <c r="E31" s="7">
@@ -1911,11 +1825,11 @@
         <v/>
       </c>
       <c r="F31" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="G31" s="7">
-        <f>(C31+E31)/2+(D31-F31)/(2*$B$5)</f>
+        <f>(D31-F31)/(2*$B$5)+(C31+E31)/2</f>
         <v/>
       </c>
       <c r="H31" s="7">
@@ -1923,22 +1837,18 @@
         <v/>
       </c>
       <c r="I31" s="7">
-        <f>MIN($B$7,$B$8,K$10:K30)</f>
+        <f>G31+SIN(3.14159*G31)</f>
         <v/>
       </c>
       <c r="J31" s="7">
         <f>I31-H31</f>
         <v/>
       </c>
-      <c r="K31" s="7">
-        <f>G31+SIN(3.14159*G31)</f>
-        <v/>
-      </c>
-      <c r="L31" s="6" t="n">
+      <c r="K31" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="M31" s="6">
-        <f>IF(J31&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L31" s="6">
+        <f>IF(J31&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -1956,7 +1866,7 @@
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>$K$19</f>
+        <f>$I$19</f>
         <v/>
       </c>
       <c r="E32" s="7">
@@ -1964,11 +1874,11 @@
         <v/>
       </c>
       <c r="F32" s="7">
-        <f>$K$13</f>
+        <f>$I$13</f>
         <v/>
       </c>
       <c r="G32" s="7">
-        <f>(C32+E32)/2+(D32-F32)/(2*$B$5)</f>
+        <f>(D32-F32)/(2*$B$5)+(C32+E32)/2</f>
         <v/>
       </c>
       <c r="H32" s="7">
@@ -1976,22 +1886,18 @@
         <v/>
       </c>
       <c r="I32" s="7">
-        <f>MIN($B$7,$B$8,K$10:K31)</f>
+        <f>G32+SIN(3.14159*G32)</f>
         <v/>
       </c>
       <c r="J32" s="7">
         <f>I32-H32</f>
         <v/>
       </c>
-      <c r="K32" s="7">
-        <f>G32+SIN(3.14159*G32)</f>
-        <v/>
-      </c>
-      <c r="L32" s="6" t="n">
+      <c r="K32" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="M32" s="6">
-        <f>IF(J32&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L32" s="6">
+        <f>IF(J32&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2009,7 +1915,7 @@
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>$K$17</f>
+        <f>$I$17</f>
         <v/>
       </c>
       <c r="E33" s="7">
@@ -2017,11 +1923,11 @@
         <v/>
       </c>
       <c r="F33" s="7">
-        <f>$K$19</f>
+        <f>$I$19</f>
         <v/>
       </c>
       <c r="G33" s="7">
-        <f>(C33+E33)/2+(D33-F33)/(2*$B$5)</f>
+        <f>(D33-F33)/(2*$B$5)+(C33+E33)/2</f>
         <v/>
       </c>
       <c r="H33" s="7">
@@ -2029,22 +1935,18 @@
         <v/>
       </c>
       <c r="I33" s="7">
-        <f>MIN($B$7,$B$8,K$10:K32)</f>
+        <f>G33+SIN(3.14159*G33)</f>
         <v/>
       </c>
       <c r="J33" s="7">
         <f>I33-H33</f>
         <v/>
       </c>
-      <c r="K33" s="7">
-        <f>G33+SIN(3.14159*G33)</f>
-        <v/>
-      </c>
-      <c r="L33" s="6" t="n">
+      <c r="K33" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="M33" s="6">
-        <f>IF(J33&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L33" s="6">
+        <f>IF(J33&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2062,7 +1964,7 @@
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>$K$26</f>
+        <f>$I$26</f>
         <v/>
       </c>
       <c r="E34" s="7">
@@ -2070,11 +1972,11 @@
         <v/>
       </c>
       <c r="F34" s="7">
-        <f>$K$22</f>
+        <f>$I$22</f>
         <v/>
       </c>
       <c r="G34" s="7">
-        <f>(C34+E34)/2+(D34-F34)/(2*$B$5)</f>
+        <f>(D34-F34)/(2*$B$5)+(C34+E34)/2</f>
         <v/>
       </c>
       <c r="H34" s="7">
@@ -2082,22 +1984,18 @@
         <v/>
       </c>
       <c r="I34" s="7">
-        <f>MIN($B$7,$B$8,K$10:K33)</f>
+        <f>G34+SIN(3.14159*G34)</f>
         <v/>
       </c>
       <c r="J34" s="7">
         <f>I34-H34</f>
         <v/>
       </c>
-      <c r="K34" s="7">
-        <f>G34+SIN(3.14159*G34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="6" t="n">
+      <c r="K34" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="M34" s="6">
-        <f>IF(J34&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L34" s="6">
+        <f>IF(J34&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2115,7 +2013,7 @@
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="E35" s="7">
@@ -2123,11 +2021,11 @@
         <v/>
       </c>
       <c r="F35" s="7">
-        <f>$K$26</f>
+        <f>$I$26</f>
         <v/>
       </c>
       <c r="G35" s="7">
-        <f>(C35+E35)/2+(D35-F35)/(2*$B$5)</f>
+        <f>(D35-F35)/(2*$B$5)+(C35+E35)/2</f>
         <v/>
       </c>
       <c r="H35" s="7">
@@ -2135,22 +2033,18 @@
         <v/>
       </c>
       <c r="I35" s="7">
-        <f>MIN($B$7,$B$8,K$10:K34)</f>
+        <f>G35+SIN(3.14159*G35)</f>
         <v/>
       </c>
       <c r="J35" s="7">
         <f>I35-H35</f>
         <v/>
       </c>
-      <c r="K35" s="7">
-        <f>G35+SIN(3.14159*G35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="6" t="n">
+      <c r="K35" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="M35" s="6">
-        <f>IF(J35&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L35" s="6">
+        <f>IF(J35&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2168,7 +2062,7 @@
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>$K$22</f>
+        <f>$I$22</f>
         <v/>
       </c>
       <c r="E36" s="7">
@@ -2176,11 +2070,11 @@
         <v/>
       </c>
       <c r="F36" s="7">
-        <f>$K$27</f>
+        <f>$I$27</f>
         <v/>
       </c>
       <c r="G36" s="7">
-        <f>(C36+E36)/2+(D36-F36)/(2*$B$5)</f>
+        <f>(D36-F36)/(2*$B$5)+(C36+E36)/2</f>
         <v/>
       </c>
       <c r="H36" s="7">
@@ -2188,22 +2082,18 @@
         <v/>
       </c>
       <c r="I36" s="7">
-        <f>MIN($B$7,$B$8,K$10:K35)</f>
+        <f>G36+SIN(3.14159*G36)</f>
         <v/>
       </c>
       <c r="J36" s="7">
         <f>I36-H36</f>
         <v/>
       </c>
-      <c r="K36" s="7">
-        <f>G36+SIN(3.14159*G36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="6" t="n">
+      <c r="K36" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="M36" s="6">
-        <f>IF(J36&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L36" s="6">
+        <f>IF(J36&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2221,7 +2111,7 @@
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>$K$27</f>
+        <f>$I$27</f>
         <v/>
       </c>
       <c r="E37" s="7">
@@ -2229,11 +2119,11 @@
         <v/>
       </c>
       <c r="F37" s="7">
-        <f>$K$18</f>
+        <f>$I$18</f>
         <v/>
       </c>
       <c r="G37" s="7">
-        <f>(C37+E37)/2+(D37-F37)/(2*$B$5)</f>
+        <f>(D37-F37)/(2*$B$5)+(C37+E37)/2</f>
         <v/>
       </c>
       <c r="H37" s="7">
@@ -2241,22 +2131,18 @@
         <v/>
       </c>
       <c r="I37" s="7">
-        <f>MIN($B$7,$B$8,K$10:K36)</f>
+        <f>G37+SIN(3.14159*G37)</f>
         <v/>
       </c>
       <c r="J37" s="7">
         <f>I37-H37</f>
         <v/>
       </c>
-      <c r="K37" s="7">
-        <f>G37+SIN(3.14159*G37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="6" t="n">
+      <c r="K37" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="M37" s="6">
-        <f>IF(J37&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L37" s="6">
+        <f>IF(J37&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2274,7 +2160,7 @@
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>$K$16</f>
+        <f>$I$16</f>
         <v/>
       </c>
       <c r="E38" s="7">
@@ -2282,11 +2168,11 @@
         <v/>
       </c>
       <c r="F38" s="7">
-        <f>$K$24</f>
+        <f>$I$24</f>
         <v/>
       </c>
       <c r="G38" s="7">
-        <f>(C38+E38)/2+(D38-F38)/(2*$B$5)</f>
+        <f>(D38-F38)/(2*$B$5)+(C38+E38)/2</f>
         <v/>
       </c>
       <c r="H38" s="7">
@@ -2294,22 +2180,18 @@
         <v/>
       </c>
       <c r="I38" s="7">
-        <f>MIN($B$7,$B$8,K$10:K37)</f>
+        <f>G38+SIN(3.14159*G38)</f>
         <v/>
       </c>
       <c r="J38" s="7">
         <f>I38-H38</f>
         <v/>
       </c>
-      <c r="K38" s="7">
-        <f>G38+SIN(3.14159*G38)</f>
-        <v/>
-      </c>
-      <c r="L38" s="6" t="n">
+      <c r="K38" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="M38" s="6">
-        <f>IF(J38&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L38" s="6">
+        <f>IF(J38&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2327,7 +2209,7 @@
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>$K$24</f>
+        <f>$I$24</f>
         <v/>
       </c>
       <c r="E39" s="7">
@@ -2335,11 +2217,11 @@
         <v/>
       </c>
       <c r="F39" s="7">
-        <f>$K$21</f>
+        <f>$I$21</f>
         <v/>
       </c>
       <c r="G39" s="7">
-        <f>(C39+E39)/2+(D39-F39)/(2*$B$5)</f>
+        <f>(D39-F39)/(2*$B$5)+(C39+E39)/2</f>
         <v/>
       </c>
       <c r="H39" s="7">
@@ -2347,22 +2229,18 @@
         <v/>
       </c>
       <c r="I39" s="7">
-        <f>MIN($B$7,$B$8,K$10:K38)</f>
+        <f>G39+SIN(3.14159*G39)</f>
         <v/>
       </c>
       <c r="J39" s="7">
         <f>I39-H39</f>
         <v/>
       </c>
-      <c r="K39" s="7">
-        <f>G39+SIN(3.14159*G39)</f>
-        <v/>
-      </c>
-      <c r="L39" s="6" t="n">
+      <c r="K39" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="M39" s="6">
-        <f>IF(J39&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L39" s="6">
+        <f>IF(J39&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2380,7 +2258,7 @@
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>$K$25</f>
+        <f>$I$25</f>
         <v/>
       </c>
       <c r="E40" s="7">
@@ -2388,11 +2266,11 @@
         <v/>
       </c>
       <c r="F40" s="7">
-        <f>$K$31</f>
+        <f>$I$31</f>
         <v/>
       </c>
       <c r="G40" s="7">
-        <f>(C40+E40)/2+(D40-F40)/(2*$B$5)</f>
+        <f>(D40-F40)/(2*$B$5)+(C40+E40)/2</f>
         <v/>
       </c>
       <c r="H40" s="7">
@@ -2400,22 +2278,18 @@
         <v/>
       </c>
       <c r="I40" s="7">
-        <f>MIN($B$7,$B$8,K$10:K39)</f>
+        <f>G40+SIN(3.14159*G40)</f>
         <v/>
       </c>
       <c r="J40" s="7">
         <f>I40-H40</f>
         <v/>
       </c>
-      <c r="K40" s="7">
-        <f>G40+SIN(3.14159*G40)</f>
-        <v/>
-      </c>
-      <c r="L40" s="6" t="n">
+      <c r="K40" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="M40" s="6">
-        <f>IF(J40&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L40" s="6">
+        <f>IF(J40&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2433,7 +2307,7 @@
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>$K$31</f>
+        <f>$I$31</f>
         <v/>
       </c>
       <c r="E41" s="7">
@@ -2441,11 +2315,11 @@
         <v/>
       </c>
       <c r="F41" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="G41" s="7">
-        <f>(C41+E41)/2+(D41-F41)/(2*$B$5)</f>
+        <f>(D41-F41)/(2*$B$5)+(C41+E41)/2</f>
         <v/>
       </c>
       <c r="H41" s="7">
@@ -2453,22 +2327,18 @@
         <v/>
       </c>
       <c r="I41" s="7">
-        <f>MIN($B$7,$B$8,K$10:K40)</f>
+        <f>G41+SIN(3.14159*G41)</f>
         <v/>
       </c>
       <c r="J41" s="7">
         <f>I41-H41</f>
         <v/>
       </c>
-      <c r="K41" s="7">
-        <f>G41+SIN(3.14159*G41)</f>
-        <v/>
-      </c>
-      <c r="L41" s="6" t="n">
+      <c r="K41" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="M41" s="6">
-        <f>IF(J41&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L41" s="6">
+        <f>IF(J41&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2486,7 +2356,7 @@
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>$K$18</f>
+        <f>$I$18</f>
         <v/>
       </c>
       <c r="E42" s="7">
@@ -2494,11 +2364,11 @@
         <v/>
       </c>
       <c r="F42" s="7">
-        <f>$K$28</f>
+        <f>$I$28</f>
         <v/>
       </c>
       <c r="G42" s="7">
-        <f>(C42+E42)/2+(D42-F42)/(2*$B$5)</f>
+        <f>(D42-F42)/(2*$B$5)+(C42+E42)/2</f>
         <v/>
       </c>
       <c r="H42" s="7">
@@ -2506,22 +2376,18 @@
         <v/>
       </c>
       <c r="I42" s="7">
-        <f>MIN($B$7,$B$8,K$10:K41)</f>
+        <f>G42+SIN(3.14159*G42)</f>
         <v/>
       </c>
       <c r="J42" s="7">
         <f>I42-H42</f>
         <v/>
       </c>
-      <c r="K42" s="7">
-        <f>G42+SIN(3.14159*G42)</f>
-        <v/>
-      </c>
-      <c r="L42" s="6" t="n">
+      <c r="K42" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="M42" s="6">
-        <f>IF(J42&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L42" s="6">
+        <f>IF(J42&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2539,7 +2405,7 @@
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>$K$28</f>
+        <f>$I$28</f>
         <v/>
       </c>
       <c r="E43" s="7">
@@ -2547,11 +2413,11 @@
         <v/>
       </c>
       <c r="F43" s="7">
-        <f>$K$23</f>
+        <f>$I$23</f>
         <v/>
       </c>
       <c r="G43" s="7">
-        <f>(C43+E43)/2+(D43-F43)/(2*$B$5)</f>
+        <f>(D43-F43)/(2*$B$5)+(C43+E43)/2</f>
         <v/>
       </c>
       <c r="H43" s="7">
@@ -2559,22 +2425,18 @@
         <v/>
       </c>
       <c r="I43" s="7">
-        <f>MIN($B$7,$B$8,K$10:K42)</f>
+        <f>G43+SIN(3.14159*G43)</f>
         <v/>
       </c>
       <c r="J43" s="7">
         <f>I43-H43</f>
         <v/>
       </c>
-      <c r="K43" s="7">
-        <f>G43+SIN(3.14159*G43)</f>
-        <v/>
-      </c>
-      <c r="L43" s="6" t="n">
+      <c r="K43" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="M43" s="6">
-        <f>IF(J43&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L43" s="6">
+        <f>IF(J43&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2592,7 +2454,7 @@
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>$K$30</f>
+        <f>$I$30</f>
         <v/>
       </c>
       <c r="E44" s="7">
@@ -2600,11 +2462,11 @@
         <v/>
       </c>
       <c r="F44" s="7">
-        <f>$K$25</f>
+        <f>$I$25</f>
         <v/>
       </c>
       <c r="G44" s="7">
-        <f>(C44+E44)/2+(D44-F44)/(2*$B$5)</f>
+        <f>(D44-F44)/(2*$B$5)+(C44+E44)/2</f>
         <v/>
       </c>
       <c r="H44" s="7">
@@ -2612,22 +2474,18 @@
         <v/>
       </c>
       <c r="I44" s="7">
-        <f>MIN($B$7,$B$8,K$10:K43)</f>
+        <f>G44+SIN(3.14159*G44)</f>
         <v/>
       </c>
       <c r="J44" s="7">
         <f>I44-H44</f>
         <v/>
       </c>
-      <c r="K44" s="7">
-        <f>G44+SIN(3.14159*G44)</f>
-        <v/>
-      </c>
-      <c r="L44" s="6" t="n">
+      <c r="K44" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="M44" s="6">
-        <f>IF(J44&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L44" s="6">
+        <f>IF(J44&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2645,7 +2503,7 @@
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>$K$21</f>
+        <f>$I$21</f>
         <v/>
       </c>
       <c r="E45" s="7">
@@ -2653,11 +2511,11 @@
         <v/>
       </c>
       <c r="F45" s="7">
-        <f>$K$30</f>
+        <f>$I$30</f>
         <v/>
       </c>
       <c r="G45" s="7">
-        <f>(C45+E45)/2+(D45-F45)/(2*$B$5)</f>
+        <f>(D45-F45)/(2*$B$5)+(C45+E45)/2</f>
         <v/>
       </c>
       <c r="H45" s="7">
@@ -2665,22 +2523,18 @@
         <v/>
       </c>
       <c r="I45" s="7">
-        <f>MIN($B$7,$B$8,K$10:K44)</f>
+        <f>G45+SIN(3.14159*G45)</f>
         <v/>
       </c>
       <c r="J45" s="7">
         <f>I45-H45</f>
         <v/>
       </c>
-      <c r="K45" s="7">
-        <f>G45+SIN(3.14159*G45)</f>
-        <v/>
-      </c>
-      <c r="L45" s="6" t="n">
+      <c r="K45" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="M45" s="6">
-        <f>IF(J45&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L45" s="6">
+        <f>IF(J45&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2698,7 +2552,7 @@
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>$K$26</f>
+        <f>$I$26</f>
         <v/>
       </c>
       <c r="E46" s="7">
@@ -2706,11 +2560,11 @@
         <v/>
       </c>
       <c r="F46" s="7">
-        <f>$K$34</f>
+        <f>$I$34</f>
         <v/>
       </c>
       <c r="G46" s="7">
-        <f>(C46+E46)/2+(D46-F46)/(2*$B$5)</f>
+        <f>(D46-F46)/(2*$B$5)+(C46+E46)/2</f>
         <v/>
       </c>
       <c r="H46" s="7">
@@ -2718,22 +2572,18 @@
         <v/>
       </c>
       <c r="I46" s="7">
-        <f>MIN($B$7,$B$8,K$10:K45)</f>
+        <f>G46+SIN(3.14159*G46)</f>
         <v/>
       </c>
       <c r="J46" s="7">
         <f>I46-H46</f>
         <v/>
       </c>
-      <c r="K46" s="7">
-        <f>G46+SIN(3.14159*G46)</f>
-        <v/>
-      </c>
-      <c r="L46" s="6" t="n">
+      <c r="K46" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="M46" s="6">
-        <f>IF(J46&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L46" s="6">
+        <f>IF(J46&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2751,7 +2601,7 @@
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>$K$34</f>
+        <f>$I$34</f>
         <v/>
       </c>
       <c r="E47" s="7">
@@ -2759,11 +2609,11 @@
         <v/>
       </c>
       <c r="F47" s="7">
-        <f>$K$22</f>
+        <f>$I$22</f>
         <v/>
       </c>
       <c r="G47" s="7">
-        <f>(C47+E47)/2+(D47-F47)/(2*$B$5)</f>
+        <f>(D47-F47)/(2*$B$5)+(C47+E47)/2</f>
         <v/>
       </c>
       <c r="H47" s="7">
@@ -2771,22 +2621,18 @@
         <v/>
       </c>
       <c r="I47" s="7">
-        <f>MIN($B$7,$B$8,K$10:K46)</f>
+        <f>G47+SIN(3.14159*G47)</f>
         <v/>
       </c>
       <c r="J47" s="7">
         <f>I47-H47</f>
         <v/>
       </c>
-      <c r="K47" s="7">
-        <f>G47+SIN(3.14159*G47)</f>
-        <v/>
-      </c>
-      <c r="L47" s="6" t="n">
+      <c r="K47" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="M47" s="6">
-        <f>IF(J47&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L47" s="6">
+        <f>IF(J47&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2804,7 +2650,7 @@
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>$K$14</f>
+        <f>$I$14</f>
         <v/>
       </c>
       <c r="E48" s="7">
@@ -2812,11 +2658,11 @@
         <v/>
       </c>
       <c r="F48" s="7">
-        <f>$K$35</f>
+        <f>$I$35</f>
         <v/>
       </c>
       <c r="G48" s="7">
-        <f>(C48+E48)/2+(D48-F48)/(2*$B$5)</f>
+        <f>(D48-F48)/(2*$B$5)+(C48+E48)/2</f>
         <v/>
       </c>
       <c r="H48" s="7">
@@ -2824,22 +2670,18 @@
         <v/>
       </c>
       <c r="I48" s="7">
-        <f>MIN($B$7,$B$8,K$10:K47)</f>
+        <f>G48+SIN(3.14159*G48)</f>
         <v/>
       </c>
       <c r="J48" s="7">
         <f>I48-H48</f>
         <v/>
       </c>
-      <c r="K48" s="7">
-        <f>G48+SIN(3.14159*G48)</f>
-        <v/>
-      </c>
-      <c r="L48" s="6" t="n">
+      <c r="K48" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="M48" s="6">
-        <f>IF(J48&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L48" s="6">
+        <f>IF(J48&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2857,7 +2699,7 @@
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>$K$35</f>
+        <f>$I$35</f>
         <v/>
       </c>
       <c r="E49" s="7">
@@ -2865,11 +2707,11 @@
         <v/>
       </c>
       <c r="F49" s="7">
-        <f>$K$26</f>
+        <f>$I$26</f>
         <v/>
       </c>
       <c r="G49" s="7">
-        <f>(C49+E49)/2+(D49-F49)/(2*$B$5)</f>
+        <f>(D49-F49)/(2*$B$5)+(C49+E49)/2</f>
         <v/>
       </c>
       <c r="H49" s="7">
@@ -2877,22 +2719,18 @@
         <v/>
       </c>
       <c r="I49" s="7">
-        <f>MIN($B$7,$B$8,K$10:K48)</f>
+        <f>G49+SIN(3.14159*G49)</f>
         <v/>
       </c>
       <c r="J49" s="7">
         <f>I49-H49</f>
         <v/>
       </c>
-      <c r="K49" s="7">
-        <f>G49+SIN(3.14159*G49)</f>
-        <v/>
-      </c>
-      <c r="L49" s="6" t="n">
+      <c r="K49" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="M49" s="6">
-        <f>IF(J49&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L49" s="6">
+        <f>IF(J49&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2910,7 +2748,7 @@
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>$K$22</f>
+        <f>$I$22</f>
         <v/>
       </c>
       <c r="E50" s="7">
@@ -2918,11 +2756,11 @@
         <v/>
       </c>
       <c r="F50" s="7">
-        <f>$K$36</f>
+        <f>$I$36</f>
         <v/>
       </c>
       <c r="G50" s="7">
-        <f>(C50+E50)/2+(D50-F50)/(2*$B$5)</f>
+        <f>(D50-F50)/(2*$B$5)+(C50+E50)/2</f>
         <v/>
       </c>
       <c r="H50" s="7">
@@ -2930,22 +2768,18 @@
         <v/>
       </c>
       <c r="I50" s="7">
-        <f>MIN($B$7,$B$8,K$10:K49)</f>
+        <f>G50+SIN(3.14159*G50)</f>
         <v/>
       </c>
       <c r="J50" s="7">
         <f>I50-H50</f>
         <v/>
       </c>
-      <c r="K50" s="7">
-        <f>G50+SIN(3.14159*G50)</f>
-        <v/>
-      </c>
-      <c r="L50" s="6" t="n">
+      <c r="K50" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="M50" s="6">
-        <f>IF(J50&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L50" s="6">
+        <f>IF(J50&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -2963,7 +2797,7 @@
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>$K$36</f>
+        <f>$I$36</f>
         <v/>
       </c>
       <c r="E51" s="7">
@@ -2971,11 +2805,11 @@
         <v/>
       </c>
       <c r="F51" s="7">
-        <f>$K$27</f>
+        <f>$I$27</f>
         <v/>
       </c>
       <c r="G51" s="7">
-        <f>(C51+E51)/2+(D51-F51)/(2*$B$5)</f>
+        <f>(D51-F51)/(2*$B$5)+(C51+E51)/2</f>
         <v/>
       </c>
       <c r="H51" s="7">
@@ -2983,22 +2817,18 @@
         <v/>
       </c>
       <c r="I51" s="7">
-        <f>MIN($B$7,$B$8,K$10:K50)</f>
+        <f>G51+SIN(3.14159*G51)</f>
         <v/>
       </c>
       <c r="J51" s="7">
         <f>I51-H51</f>
         <v/>
       </c>
-      <c r="K51" s="7">
-        <f>G51+SIN(3.14159*G51)</f>
-        <v/>
-      </c>
-      <c r="L51" s="6" t="n">
+      <c r="K51" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="M51" s="6">
-        <f>IF(J51&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L51" s="6">
+        <f>IF(J51&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -3016,7 +2846,7 @@
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>$K$20</f>
+        <f>$I$20</f>
         <v/>
       </c>
       <c r="E52" s="7">
@@ -3024,11 +2854,11 @@
         <v/>
       </c>
       <c r="F52" s="7">
-        <f>$K$16</f>
+        <f>$I$16</f>
         <v/>
       </c>
       <c r="G52" s="7">
-        <f>(C52+E52)/2+(D52-F52)/(2*$B$5)</f>
+        <f>(D52-F52)/(2*$B$5)+(C52+E52)/2</f>
         <v/>
       </c>
       <c r="H52" s="7">
@@ -3036,22 +2866,18 @@
         <v/>
       </c>
       <c r="I52" s="7">
-        <f>MIN($B$7,$B$8,K$10:K51)</f>
+        <f>G52+SIN(3.14159*G52)</f>
         <v/>
       </c>
       <c r="J52" s="7">
         <f>I52-H52</f>
         <v/>
       </c>
-      <c r="K52" s="7">
-        <f>G52+SIN(3.14159*G52)</f>
-        <v/>
-      </c>
-      <c r="L52" s="6" t="n">
+      <c r="K52" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="M52" s="6">
-        <f>IF(J52&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L52" s="6">
+        <f>IF(J52&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -3077,11 +2903,11 @@
         <v/>
       </c>
       <c r="F53" s="7">
-        <f>$K$20</f>
+        <f>$I$20</f>
         <v/>
       </c>
       <c r="G53" s="7">
-        <f>(C53+E53)/2+(D53-F53)/(2*$B$5)</f>
+        <f>(D53-F53)/(2*$B$5)+(C53+E53)/2</f>
         <v/>
       </c>
       <c r="H53" s="7">
@@ -3089,22 +2915,18 @@
         <v/>
       </c>
       <c r="I53" s="7">
-        <f>MIN($B$7,$B$8,K$10:K52)</f>
+        <f>G53+SIN(3.14159*G53)</f>
         <v/>
       </c>
       <c r="J53" s="7">
         <f>I53-H53</f>
         <v/>
       </c>
-      <c r="K53" s="7">
-        <f>G53+SIN(3.14159*G53)</f>
-        <v/>
-      </c>
-      <c r="L53" s="6" t="n">
+      <c r="K53" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="M53" s="6">
-        <f>IF(J53&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L53" s="6">
+        <f>IF(J53&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -3122,7 +2944,7 @@
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>$K$27</f>
+        <f>$I$27</f>
         <v/>
       </c>
       <c r="E54" s="7">
@@ -3130,11 +2952,11 @@
         <v/>
       </c>
       <c r="F54" s="7">
-        <f>$K$37</f>
+        <f>$I$37</f>
         <v/>
       </c>
       <c r="G54" s="7">
-        <f>(C54+E54)/2+(D54-F54)/(2*$B$5)</f>
+        <f>(D54-F54)/(2*$B$5)+(C54+E54)/2</f>
         <v/>
       </c>
       <c r="H54" s="7">
@@ -3142,22 +2964,18 @@
         <v/>
       </c>
       <c r="I54" s="7">
-        <f>MIN($B$7,$B$8,K$10:K53)</f>
+        <f>G54+SIN(3.14159*G54)</f>
         <v/>
       </c>
       <c r="J54" s="7">
         <f>I54-H54</f>
         <v/>
       </c>
-      <c r="K54" s="7">
-        <f>G54+SIN(3.14159*G54)</f>
-        <v/>
-      </c>
-      <c r="L54" s="6" t="n">
+      <c r="K54" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="M54" s="6">
-        <f>IF(J54&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L54" s="6">
+        <f>IF(J54&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
@@ -3175,7 +2993,7 @@
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>$K$37</f>
+        <f>$I$37</f>
         <v/>
       </c>
       <c r="E55" s="7">
@@ -3183,11 +3001,11 @@
         <v/>
       </c>
       <c r="F55" s="7">
-        <f>$K$18</f>
+        <f>$I$18</f>
         <v/>
       </c>
       <c r="G55" s="7">
-        <f>(C55+E55)/2+(D55-F55)/(2*$B$5)</f>
+        <f>(D55-F55)/(2*$B$5)+(C55+E55)/2</f>
         <v/>
       </c>
       <c r="H55" s="7">
@@ -3195,121 +3013,314 @@
         <v/>
       </c>
       <c r="I55" s="7">
-        <f>MIN($B$7,$B$8,K$10:K54)</f>
+        <f>G55+SIN(3.14159*G55)</f>
         <v/>
       </c>
       <c r="J55" s="7">
         <f>I55-H55</f>
         <v/>
       </c>
-      <c r="K55" s="7">
-        <f>G55+SIN(3.14159*G55)</f>
-        <v/>
-      </c>
-      <c r="L55" s="6" t="n">
+      <c r="K55" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="M55" s="6">
-        <f>IF(J55&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="L55" s="6">
+        <f>IF(J55&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n">
+      <c r="A56" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>22 и 32</t>
         </is>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="7">
         <f>$G$31</f>
         <v/>
       </c>
-      <c r="D56" s="9">
-        <f>$K$31</f>
-        <v/>
-      </c>
-      <c r="E56" s="9">
+      <c r="D56" s="7">
+        <f>$I$31</f>
+        <v/>
+      </c>
+      <c r="E56" s="7">
         <f>$G$41</f>
         <v/>
       </c>
-      <c r="F56" s="9">
-        <f>$K$41</f>
-        <v/>
-      </c>
-      <c r="G56" s="9">
-        <f>(C56+E56)/2+(D56-F56)/(2*$B$5)</f>
-        <v/>
-      </c>
-      <c r="H56" s="9">
+      <c r="F56" s="7">
+        <f>$I$41</f>
+        <v/>
+      </c>
+      <c r="G56" s="7">
+        <f>(D56-F56)/(2*$B$5)+(C56+E56)/2</f>
+        <v/>
+      </c>
+      <c r="H56" s="7">
         <f>(D56+F56)/2-$B$5*(E56-C56)/2</f>
         <v/>
       </c>
-      <c r="I56" s="9">
-        <f>MIN($B$7,$B$8,K$10:K55)</f>
-        <v/>
-      </c>
-      <c r="J56" s="9">
+      <c r="I56" s="7">
+        <f>G56+SIN(3.14159*G56)</f>
+        <v/>
+      </c>
+      <c r="J56" s="7">
         <f>I56-H56</f>
         <v/>
       </c>
-      <c r="K56" s="9" t="n"/>
-      <c r="L56" s="8" t="n"/>
-      <c r="M56" s="8">
-        <f>IF(J56&lt;=$B$6,"СТОП: f*-p̂ &lt;= eps","испытание")</f>
+      <c r="K56" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="L56" s="6">
+        <f>IF(J56&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>32 и 5</t>
+        </is>
+      </c>
+      <c r="C57" s="7">
+        <f>$G$41</f>
+        <v/>
+      </c>
+      <c r="D57" s="7">
+        <f>$I$41</f>
+        <v/>
+      </c>
+      <c r="E57" s="7">
+        <f>$G$14</f>
+        <v/>
+      </c>
+      <c r="F57" s="7">
+        <f>$I$14</f>
+        <v/>
+      </c>
+      <c r="G57" s="7">
+        <f>(D57-F57)/(2*$B$5)+(C57+E57)/2</f>
+        <v/>
+      </c>
+      <c r="H57" s="7">
+        <f>(D57+F57)/2-$B$5*(E57-C57)/2</f>
+        <v/>
+      </c>
+      <c r="I57" s="7">
+        <f>G57+SIN(3.14159*G57)</f>
+        <v/>
+      </c>
+      <c r="J57" s="7">
+        <f>I57-H57</f>
+        <v/>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="L57" s="6">
+        <f>IF(J57&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>16 и 31</t>
+        </is>
+      </c>
+      <c r="C58" s="7">
+        <f>$G$25</f>
+        <v/>
+      </c>
+      <c r="D58" s="7">
+        <f>$I$25</f>
+        <v/>
+      </c>
+      <c r="E58" s="7">
+        <f>$G$40</f>
+        <v/>
+      </c>
+      <c r="F58" s="7">
+        <f>$I$40</f>
+        <v/>
+      </c>
+      <c r="G58" s="7">
+        <f>(D58-F58)/(2*$B$5)+(C58+E58)/2</f>
+        <v/>
+      </c>
+      <c r="H58" s="7">
+        <f>(D58+F58)/2-$B$5*(E58-C58)/2</f>
+        <v/>
+      </c>
+      <c r="I58" s="7">
+        <f>G58+SIN(3.14159*G58)</f>
+        <v/>
+      </c>
+      <c r="J58" s="7">
+        <f>I58-H58</f>
+        <v/>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="L58" s="6">
+        <f>IF(J58&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>31 и 22</t>
+        </is>
+      </c>
+      <c r="C59" s="7">
+        <f>$G$40</f>
+        <v/>
+      </c>
+      <c r="D59" s="7">
+        <f>$I$40</f>
+        <v/>
+      </c>
+      <c r="E59" s="7">
+        <f>$G$31</f>
+        <v/>
+      </c>
+      <c r="F59" s="7">
+        <f>$I$31</f>
+        <v/>
+      </c>
+      <c r="G59" s="7">
+        <f>(D59-F59)/(2*$B$5)+(C59+E59)/2</f>
+        <v/>
+      </c>
+      <c r="H59" s="7">
+        <f>(D59+F59)/2-$B$5*(E59-C59)/2</f>
+        <v/>
+      </c>
+      <c r="I59" s="7">
+        <f>G59+SIN(3.14159*G59)</f>
+        <v/>
+      </c>
+      <c r="J59" s="7">
+        <f>I59-H59</f>
+        <v/>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="L59" s="6">
+        <f>IF(J59&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>17 и 37</t>
+        </is>
+      </c>
+      <c r="C60" s="9">
+        <f>$G$26</f>
+        <v/>
+      </c>
+      <c r="D60" s="9">
+        <f>$I$26</f>
+        <v/>
+      </c>
+      <c r="E60" s="9">
+        <f>$G$46</f>
+        <v/>
+      </c>
+      <c r="F60" s="9">
+        <f>$I$46</f>
+        <v/>
+      </c>
+      <c r="G60" s="9">
+        <f>(D60-F60)/(2*$B$5)+(C60+E60)/2</f>
+        <v/>
+      </c>
+      <c r="H60" s="9">
+        <f>(D60+F60)/2-$B$5*(E60-C60)/2</f>
+        <v/>
+      </c>
+      <c r="I60" s="9">
+        <f>G60+SIN(3.14159*G60)</f>
+        <v/>
+      </c>
+      <c r="J60" s="9">
+        <f>I60-H60</f>
+        <v/>
+      </c>
+      <c r="K60" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="L60" s="8">
+        <f>IF(J60&lt;$B$6,"СТОП: W(u)-p(u) &lt; eps","продолжаем")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Ответ</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>f(x*) ≈</t>
-        </is>
-      </c>
-      <c r="B59" s="11">
-        <f>I56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>x* ≈</t>
-        </is>
-      </c>
-      <c r="B60" s="11">
-        <f>INDEX(G11:G55,MATCH(I56,K11:K55,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>итераций</t>
-        </is>
-      </c>
-      <c r="B61" s="12">
-        <f>COUNT(K11:K56)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>точность f* − p̂</t>
-        </is>
-      </c>
-      <c r="B62" s="11">
-        <f>J56</f>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>u* ≈</t>
+        </is>
+      </c>
+      <c r="B63" s="11">
+        <f>G60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>W(u*) ≈</t>
+        </is>
+      </c>
+      <c r="B64" s="11">
+        <f>I60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>итераций (после стартовых)</t>
+        </is>
+      </c>
+      <c r="B65" s="12">
+        <f>COUNT(A11:A60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>W(u*) − p(u*)</t>
+        </is>
+      </c>
+      <c r="B66" s="11">
+        <f>J60</f>
         <v/>
       </c>
     </row>
